--- a/اسماء شركات الاسنان/فيوتشر للموظفين المستوفين البيانات.xlsx
+++ b/اسماء شركات الاسنان/فيوتشر للموظفين المستوفين البيانات.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\majdi\OneDrive\سطح المكتب\PC\استدامة\بطاقات وعد القابضة\WAAD FUTURE\WAAD FUTURE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\اسماء شركات الاسنان\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F548B0AC-22FA-4447-A724-B98BA7E730D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87946F1-49A9-46BF-A051-670BC9FD16A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{49CC2BD4-6C36-4645-877C-AEFEA44D83A0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{49CC2BD4-6C36-4645-877C-AEFEA44D83A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -812,7 +812,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -832,20 +832,20 @@
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1314,59 +1314,59 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1682,48 +1682,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F51F8D0-E8F4-9848-804F-3D68FAFA0281}">
-  <dimension ref="A2:J99"/>
-  <sheetFormatPr defaultColWidth="11.4140625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:K99"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.58203125" customWidth="1"/>
-    <col min="2" max="2" width="3.58203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.54296875" customWidth="1"/>
+    <col min="2" max="2" width="3.54296875" style="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" style="25" customWidth="1"/>
-    <col min="4" max="4" width="13.4140625" style="25" customWidth="1"/>
-    <col min="5" max="5" width="14.4140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.4140625" style="25" customWidth="1"/>
-    <col min="7" max="7" width="18.9140625" style="25" customWidth="1"/>
-    <col min="8" max="8" width="13.08203125" style="25" customWidth="1"/>
-    <col min="9" max="9" width="15.25" style="26" customWidth="1"/>
-    <col min="10" max="10" width="21.9140625" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="25" customWidth="1"/>
+    <col min="7" max="7" width="18.90625" style="25" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" style="25" customWidth="1"/>
+    <col min="9" max="9" width="15.26953125" style="26" customWidth="1"/>
+    <col min="10" max="10" width="21.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C2" s="49" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C2" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-    </row>
-    <row r="3" spans="1:10" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="47" t="s">
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+    </row>
+    <row r="3" spans="1:11" ht="22.8" x14ac:dyDescent="0.25">
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="I3" s="47"/>
-    </row>
-    <row r="4" spans="1:10" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H4" s="48" t="s">
+      <c r="I3" s="36"/>
+    </row>
+    <row r="4" spans="1:11" ht="23.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H4" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="I4" s="48"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I4" s="37"/>
+    </row>
+    <row r="5" spans="1:11" ht="26.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="8">
         <v>1</v>
       </c>
@@ -1771,18 +1771,21 @@
       <c r="I6" s="27">
         <v>37284</v>
       </c>
-      <c r="J6" s="52" t="s">
+      <c r="J6" s="35" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B7" s="8">
         <v>2</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="38">
         <v>4</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -1794,24 +1797,27 @@
       <c r="G7" s="11">
         <v>119780020983</v>
       </c>
-      <c r="H7" s="38" t="s">
+      <c r="H7" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I7" s="28">
         <v>28674</v>
       </c>
-      <c r="J7" s="52" t="s">
+      <c r="J7" s="35" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D8" s="44"/>
+      <c r="D8" s="39"/>
       <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
@@ -1821,22 +1827,25 @@
       <c r="G8" s="1">
         <v>219900353028</v>
       </c>
-      <c r="H8" s="40"/>
+      <c r="H8" s="44"/>
       <c r="I8" s="29">
         <v>33172</v>
       </c>
-      <c r="J8" s="52" t="s">
+      <c r="J8" s="35" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="D9" s="44"/>
+      <c r="D9" s="39"/>
       <c r="E9" s="1" t="s">
         <v>90</v>
       </c>
@@ -1846,22 +1855,25 @@
       <c r="G9" s="1">
         <v>220160041899</v>
       </c>
-      <c r="H9" s="40"/>
+      <c r="H9" s="44"/>
       <c r="I9" s="29">
         <v>42398</v>
       </c>
-      <c r="J9" s="52" t="s">
+      <c r="J9" s="35" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>251</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="43"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="14" t="s">
         <v>91</v>
       </c>
@@ -1871,22 +1883,25 @@
       <c r="G10" s="14">
         <v>120190740877</v>
       </c>
-      <c r="H10" s="39"/>
+      <c r="H10" s="45"/>
       <c r="I10" s="30">
         <v>43713</v>
       </c>
-      <c r="J10" s="52" t="s">
+      <c r="J10" s="35" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B11" s="8">
         <v>3</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="38">
         <v>3</v>
       </c>
       <c r="E11" s="11" t="s">
@@ -1898,24 +1913,27 @@
       <c r="G11" s="11">
         <v>219900232183</v>
       </c>
-      <c r="H11" s="38" t="s">
+      <c r="H11" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I11" s="28">
         <v>33105</v>
       </c>
-      <c r="J11" s="52" t="s">
+      <c r="J11" s="35" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="44"/>
+      <c r="D12" s="39"/>
       <c r="E12" s="1" t="s">
         <v>110</v>
       </c>
@@ -1925,22 +1943,25 @@
       <c r="G12" s="1">
         <v>119410037244</v>
       </c>
-      <c r="H12" s="40"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="29">
         <v>14977</v>
       </c>
-      <c r="J12" s="52" t="s">
+      <c r="J12" s="35" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="43"/>
+      <c r="D13" s="40"/>
       <c r="E13" s="14" t="s">
         <v>76</v>
       </c>
@@ -1950,22 +1971,25 @@
       <c r="G13" s="14">
         <v>219610095278</v>
       </c>
-      <c r="H13" s="39"/>
+      <c r="H13" s="45"/>
       <c r="I13" s="30">
         <v>22299</v>
       </c>
-      <c r="J13" s="52" t="s">
+      <c r="J13" s="35" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B14" s="8">
         <v>4</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="38">
         <v>4</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -1977,17 +2001,20 @@
       <c r="G14" s="11">
         <v>219930317047</v>
       </c>
-      <c r="H14" s="38" t="s">
+      <c r="H14" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I14" s="28">
         <v>34263</v>
       </c>
-      <c r="J14" s="52" t="s">
+      <c r="J14" s="35" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1997,7 +2024,7 @@
       <c r="C15" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="44"/>
+      <c r="D15" s="39"/>
       <c r="E15" s="1" t="s">
         <v>53</v>
       </c>
@@ -2007,22 +2034,25 @@
       <c r="G15" s="1">
         <v>119670200936</v>
       </c>
-      <c r="H15" s="40"/>
+      <c r="H15" s="44"/>
       <c r="I15" s="29">
         <v>24473</v>
       </c>
-      <c r="J15" s="52" t="s">
+      <c r="J15" s="35" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="44"/>
+      <c r="D16" s="39"/>
       <c r="E16" s="1" t="s">
         <v>54</v>
       </c>
@@ -2032,22 +2062,25 @@
       <c r="G16" s="1">
         <v>219730277370</v>
       </c>
-      <c r="H16" s="40"/>
+      <c r="H16" s="44"/>
       <c r="I16" s="29">
         <v>26777</v>
       </c>
-      <c r="J16" s="52" t="s">
+      <c r="J16" s="35" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K16">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="8" t="s">
         <v>251</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D17" s="43"/>
+      <c r="D17" s="40"/>
       <c r="E17" s="14" t="s">
         <v>45</v>
       </c>
@@ -2057,22 +2090,25 @@
       <c r="G17" s="14">
         <v>120200501641</v>
       </c>
-      <c r="H17" s="39"/>
+      <c r="H17" s="45"/>
       <c r="I17" s="30">
         <v>44038</v>
       </c>
-      <c r="J17" s="52" t="s">
+      <c r="J17" s="35" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B18" s="8">
         <v>5</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="38">
         <v>3</v>
       </c>
       <c r="E18" s="11" t="s">
@@ -2084,24 +2120,27 @@
       <c r="G18" s="11">
         <v>21995082723</v>
       </c>
-      <c r="H18" s="38" t="s">
+      <c r="H18" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I18" s="28">
         <v>34873</v>
       </c>
-      <c r="J18" s="52" t="s">
+      <c r="J18" s="35" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K18">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="D19" s="44"/>
+      <c r="D19" s="39"/>
       <c r="E19" s="1" t="s">
         <v>75</v>
       </c>
@@ -2111,22 +2150,25 @@
       <c r="G19" s="1">
         <v>119540007199</v>
       </c>
-      <c r="H19" s="40"/>
+      <c r="H19" s="44"/>
       <c r="I19" s="29">
         <v>19725</v>
       </c>
-      <c r="J19" s="52" t="s">
+      <c r="J19" s="35" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="D20" s="43"/>
+      <c r="D20" s="40"/>
       <c r="E20" s="14" t="s">
         <v>76</v>
       </c>
@@ -2136,22 +2178,25 @@
       <c r="G20" s="14">
         <v>219600202291</v>
       </c>
-      <c r="H20" s="39"/>
+      <c r="H20" s="45"/>
       <c r="I20" s="30">
         <v>22041</v>
       </c>
-      <c r="J20" s="52" t="s">
+      <c r="J20" s="35" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B21" s="8">
         <v>6</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="38">
         <v>6</v>
       </c>
       <c r="E21" s="11" t="s">
@@ -2163,24 +2208,27 @@
       <c r="G21" s="11">
         <v>119910080854</v>
       </c>
-      <c r="H21" s="35" t="s">
+      <c r="H21" s="50" t="s">
         <v>171</v>
       </c>
       <c r="I21" s="28">
         <v>33245</v>
       </c>
-      <c r="J21" s="52" t="s">
+      <c r="J21" s="35" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="44"/>
+      <c r="D22" s="39"/>
       <c r="E22" s="1" t="s">
         <v>149</v>
       </c>
@@ -2190,22 +2238,25 @@
       <c r="G22" s="1">
         <v>219980448359</v>
       </c>
-      <c r="H22" s="36"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="29">
         <v>35873</v>
       </c>
-      <c r="J22" s="52" t="s">
+      <c r="J22" s="35" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K22">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B23" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D23" s="44"/>
+      <c r="D23" s="39"/>
       <c r="E23" s="1" t="s">
         <v>90</v>
       </c>
@@ -2215,22 +2266,25 @@
       <c r="G23" s="1">
         <v>220230790304</v>
       </c>
-      <c r="H23" s="36"/>
+      <c r="H23" s="48"/>
       <c r="I23" s="29">
         <v>45166</v>
       </c>
-      <c r="J23" s="52" t="s">
+      <c r="J23" s="35" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="24" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K23">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
         <v>251</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="D24" s="44"/>
+      <c r="D24" s="39"/>
       <c r="E24" s="1" t="s">
         <v>90</v>
       </c>
@@ -2240,22 +2294,25 @@
       <c r="G24" s="1">
         <v>220250750874</v>
       </c>
-      <c r="H24" s="36"/>
+      <c r="H24" s="48"/>
       <c r="I24" s="29">
         <v>45937</v>
       </c>
-      <c r="J24" s="52" t="s">
+      <c r="J24" s="35" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="25" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K24">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B25" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="D25" s="44"/>
+      <c r="D25" s="39"/>
       <c r="E25" s="1" t="s">
         <v>75</v>
       </c>
@@ -2265,22 +2322,25 @@
       <c r="G25" s="1">
         <v>119530106419</v>
       </c>
-      <c r="H25" s="36"/>
+      <c r="H25" s="48"/>
       <c r="I25" s="29">
         <v>19360</v>
       </c>
-      <c r="J25" s="52" t="s">
+      <c r="J25" s="35" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="8" t="s">
         <v>253</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="43"/>
+      <c r="D26" s="40"/>
       <c r="E26" s="14" t="s">
         <v>76</v>
       </c>
@@ -2290,22 +2350,25 @@
       <c r="G26" s="14">
         <v>219590176181</v>
       </c>
-      <c r="H26" s="37"/>
+      <c r="H26" s="49"/>
       <c r="I26" s="30">
         <v>21831</v>
       </c>
-      <c r="J26" s="52" t="s">
+      <c r="J26" s="35" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K26">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B27" s="8">
         <v>7</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="45">
+      <c r="D27" s="42">
         <v>7</v>
       </c>
       <c r="E27" s="4" t="s">
@@ -2317,24 +2380,27 @@
       <c r="G27" s="4">
         <v>119700249658</v>
       </c>
-      <c r="H27" s="50" t="s">
+      <c r="H27" s="46" t="s">
         <v>171</v>
       </c>
       <c r="I27" s="31">
         <v>25633</v>
       </c>
-      <c r="J27" s="52" t="s">
+      <c r="J27" s="35" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="28" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K27">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B28" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="44"/>
+      <c r="D28" s="39"/>
       <c r="E28" s="1" t="s">
         <v>24</v>
       </c>
@@ -2344,22 +2410,25 @@
       <c r="G28" s="1">
         <v>219820072249</v>
       </c>
-      <c r="H28" s="40"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="29">
         <v>30138</v>
       </c>
-      <c r="J28" s="52" t="s">
+      <c r="J28" s="35" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="29" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K28">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="44"/>
+      <c r="D29" s="39"/>
       <c r="E29" s="1" t="s">
         <v>90</v>
       </c>
@@ -2369,22 +2438,25 @@
       <c r="G29" s="1">
         <v>220070050327</v>
       </c>
-      <c r="H29" s="40"/>
+      <c r="H29" s="44"/>
       <c r="I29" s="29">
         <v>39307</v>
       </c>
-      <c r="J29" s="52" t="s">
+      <c r="J29" s="35" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="30" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B30" s="8" t="s">
         <v>251</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="44"/>
+      <c r="D30" s="39"/>
       <c r="E30" s="1" t="s">
         <v>90</v>
       </c>
@@ -2394,22 +2466,25 @@
       <c r="G30" s="1">
         <v>220110129886</v>
       </c>
-      <c r="H30" s="40"/>
+      <c r="H30" s="44"/>
       <c r="I30" s="29">
         <v>40784</v>
       </c>
-      <c r="J30" s="52" t="s">
+      <c r="J30" s="35" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="31" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K30">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B31" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="44"/>
+      <c r="D31" s="39"/>
       <c r="E31" s="1" t="s">
         <v>91</v>
       </c>
@@ -2419,22 +2494,25 @@
       <c r="G31" s="1">
         <v>120181158481</v>
       </c>
-      <c r="H31" s="40"/>
+      <c r="H31" s="44"/>
       <c r="I31" s="29">
         <v>43306</v>
       </c>
-      <c r="J31" s="52" t="s">
+      <c r="J31" s="35" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="32" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K31">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B32" s="8" t="s">
         <v>253</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="44"/>
+      <c r="D32" s="39"/>
       <c r="E32" s="1" t="s">
         <v>75</v>
       </c>
@@ -2444,22 +2522,25 @@
       <c r="G32" s="1">
         <v>119380021782</v>
       </c>
-      <c r="H32" s="40"/>
+      <c r="H32" s="44"/>
       <c r="I32" s="29">
         <v>14116</v>
       </c>
-      <c r="J32" s="52" t="s">
+      <c r="J32" s="35" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="33" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K32">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
         <v>254</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="43"/>
+      <c r="D33" s="40"/>
       <c r="E33" s="14" t="s">
         <v>76</v>
       </c>
@@ -2469,22 +2550,25 @@
       <c r="G33" s="14">
         <v>219450001310</v>
       </c>
-      <c r="H33" s="39"/>
+      <c r="H33" s="45"/>
       <c r="I33" s="30">
         <v>16438</v>
       </c>
-      <c r="J33" s="52" t="s">
+      <c r="J33" s="35" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="34" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K33">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="8">
         <v>8</v>
       </c>
       <c r="C34" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="D34" s="45">
+      <c r="D34" s="42">
         <v>4</v>
       </c>
       <c r="E34" s="4" t="s">
@@ -2496,24 +2580,27 @@
       <c r="G34" s="4">
         <v>119890398538</v>
       </c>
-      <c r="H34" s="51" t="s">
+      <c r="H34" s="47" t="s">
         <v>172</v>
       </c>
       <c r="I34" s="31">
         <v>32866</v>
       </c>
-      <c r="J34" s="52" t="s">
+      <c r="J34" s="35" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="35" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K34">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B35" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="44"/>
+      <c r="D35" s="39"/>
       <c r="E35" s="1" t="s">
         <v>24</v>
       </c>
@@ -2523,22 +2610,25 @@
       <c r="G35" s="1">
         <v>219950270494</v>
       </c>
-      <c r="H35" s="36"/>
+      <c r="H35" s="48"/>
       <c r="I35" s="29">
         <v>34909</v>
       </c>
-      <c r="J35" s="52" t="s">
+      <c r="J35" s="35" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="36" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B36" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="44"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="1" t="s">
         <v>91</v>
       </c>
@@ -2548,22 +2638,25 @@
       <c r="G36" s="1">
         <v>120211118018</v>
       </c>
-      <c r="H36" s="36"/>
+      <c r="H36" s="48"/>
       <c r="I36" s="29">
         <v>44551</v>
       </c>
-      <c r="J36" s="52" t="s">
+      <c r="J36" s="35" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="37" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K36">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="8" t="s">
         <v>251</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="43"/>
+      <c r="D37" s="40"/>
       <c r="E37" s="14" t="s">
         <v>91</v>
       </c>
@@ -2573,22 +2666,25 @@
       <c r="G37" s="14">
         <v>120240894327</v>
       </c>
-      <c r="H37" s="37"/>
+      <c r="H37" s="49"/>
       <c r="I37" s="30">
         <v>45600</v>
       </c>
-      <c r="J37" s="52" t="s">
+      <c r="J37" s="35" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="38" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K37">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B38" s="8">
         <v>9</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="42">
+      <c r="D38" s="38">
         <v>7</v>
       </c>
       <c r="E38" s="11" t="s">
@@ -2600,24 +2696,27 @@
       <c r="G38" s="11">
         <v>119800296296</v>
       </c>
-      <c r="H38" s="35" t="s">
+      <c r="H38" s="50" t="s">
         <v>171</v>
       </c>
       <c r="I38" s="28">
         <v>29560</v>
       </c>
-      <c r="J38" s="52" t="s">
+      <c r="J38" s="35" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="39" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K38">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B39" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D39" s="44"/>
+      <c r="D39" s="39"/>
       <c r="E39" s="1" t="s">
         <v>75</v>
       </c>
@@ -2627,22 +2726,25 @@
       <c r="G39" s="1">
         <v>119420061589</v>
       </c>
-      <c r="H39" s="36"/>
+      <c r="H39" s="48"/>
       <c r="I39" s="29">
         <v>15342</v>
       </c>
-      <c r="J39" s="52" t="s">
+      <c r="J39" s="35" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="40" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K39">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B40" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="D40" s="44"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="1" t="s">
         <v>76</v>
       </c>
@@ -2652,22 +2754,25 @@
       <c r="G40" s="1">
         <v>219470043646</v>
       </c>
-      <c r="H40" s="36"/>
+      <c r="H40" s="48"/>
       <c r="I40" s="29">
         <v>17168</v>
       </c>
-      <c r="J40" s="52" t="s">
+      <c r="J40" s="35" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="41" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K40">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B41" s="8" t="s">
         <v>251</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D41" s="44"/>
+      <c r="D41" s="39"/>
       <c r="E41" s="1" t="s">
         <v>89</v>
       </c>
@@ -2677,22 +2782,25 @@
       <c r="G41" s="1">
         <v>219830555925</v>
       </c>
-      <c r="H41" s="36"/>
+      <c r="H41" s="48"/>
       <c r="I41" s="29">
         <v>30625</v>
       </c>
-      <c r="J41" s="52" t="s">
+      <c r="J41" s="35" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="42" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B42" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="D42" s="44"/>
+      <c r="D42" s="39"/>
       <c r="E42" s="1" t="s">
         <v>90</v>
       </c>
@@ -2702,22 +2810,25 @@
       <c r="G42" s="1">
         <v>220140960170</v>
       </c>
-      <c r="H42" s="36"/>
+      <c r="H42" s="48"/>
       <c r="I42" s="29">
         <v>41787</v>
       </c>
-      <c r="J42" s="52" t="s">
+      <c r="J42" s="35" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="43" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K42">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B43" s="8" t="s">
         <v>253</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D43" s="44"/>
+      <c r="D43" s="39"/>
       <c r="E43" s="1" t="s">
         <v>90</v>
       </c>
@@ -2727,22 +2838,25 @@
       <c r="G43" s="1">
         <v>220110953720</v>
       </c>
-      <c r="H43" s="36"/>
+      <c r="H43" s="48"/>
       <c r="I43" s="29">
         <v>40747</v>
       </c>
-      <c r="J43" s="52" t="s">
+      <c r="J43" s="35" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="44" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K43">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="8" t="s">
         <v>254</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="43"/>
+      <c r="D44" s="40"/>
       <c r="E44" s="14" t="s">
         <v>91</v>
       </c>
@@ -2752,22 +2866,25 @@
       <c r="G44" s="14">
         <v>120170131301</v>
       </c>
-      <c r="H44" s="37"/>
+      <c r="H44" s="49"/>
       <c r="I44" s="30">
         <v>42770</v>
       </c>
-      <c r="J44" s="52" t="s">
+      <c r="J44" s="35" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="45" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K44">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B45" s="8">
         <v>10</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D45" s="42">
+      <c r="D45" s="38">
         <v>3</v>
       </c>
       <c r="E45" s="11" t="s">
@@ -2779,24 +2896,27 @@
       <c r="G45" s="11">
         <v>219990441133</v>
       </c>
-      <c r="H45" s="38" t="s">
+      <c r="H45" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I45" s="28">
         <v>36425</v>
       </c>
-      <c r="J45" s="52" t="s">
+      <c r="J45" s="35" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="46" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D46" s="44"/>
+      <c r="D46" s="39"/>
       <c r="E46" s="1" t="s">
         <v>75</v>
       </c>
@@ -2806,22 +2926,25 @@
       <c r="G46" s="1">
         <v>119640122028</v>
       </c>
-      <c r="H46" s="40"/>
+      <c r="H46" s="44"/>
       <c r="I46" s="29">
         <v>23377</v>
       </c>
-      <c r="J46" s="52" t="s">
+      <c r="J46" s="35" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="47" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K46">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="43"/>
+      <c r="D47" s="40"/>
       <c r="E47" s="14" t="s">
         <v>76</v>
       </c>
@@ -2831,22 +2954,25 @@
       <c r="G47" s="14">
         <v>219640238694</v>
       </c>
-      <c r="H47" s="39"/>
+      <c r="H47" s="45"/>
       <c r="I47" s="30">
         <v>23523</v>
       </c>
-      <c r="J47" s="52" t="s">
+      <c r="J47" s="35" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="48" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B48" s="8">
         <v>11</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D48" s="42">
+      <c r="D48" s="38">
         <v>4</v>
       </c>
       <c r="E48" s="11" t="s">
@@ -2858,24 +2984,27 @@
       <c r="G48" s="11">
         <v>119810468615</v>
       </c>
-      <c r="H48" s="38" t="s">
+      <c r="H48" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I48" s="28">
         <v>29838</v>
       </c>
-      <c r="J48" s="52" t="s">
+      <c r="J48" s="35" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="49" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B49" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D49" s="44"/>
+      <c r="D49" s="39"/>
       <c r="E49" s="1" t="s">
         <v>24</v>
       </c>
@@ -2885,22 +3014,25 @@
       <c r="G49" s="1">
         <v>219800318323</v>
       </c>
-      <c r="H49" s="40"/>
+      <c r="H49" s="44"/>
       <c r="I49" s="29">
         <v>29390</v>
       </c>
-      <c r="J49" s="52" t="s">
+      <c r="J49" s="35" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="50" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B50" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D50" s="44"/>
+      <c r="D50" s="39"/>
       <c r="E50" s="1" t="s">
         <v>91</v>
       </c>
@@ -2910,22 +3042,25 @@
       <c r="G50" s="1">
         <v>120110624184</v>
       </c>
-      <c r="H50" s="40"/>
+      <c r="H50" s="44"/>
       <c r="I50" s="29">
         <v>40627</v>
       </c>
-      <c r="J50" s="52" t="s">
+      <c r="J50" s="35" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="51" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K50">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8" t="s">
         <v>251</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D51" s="43"/>
+      <c r="D51" s="40"/>
       <c r="E51" s="14" t="s">
         <v>91</v>
       </c>
@@ -2935,15 +3070,18 @@
       <c r="G51" s="14">
         <v>120130777112</v>
       </c>
-      <c r="H51" s="39"/>
+      <c r="H51" s="45"/>
       <c r="I51" s="30">
         <v>41482</v>
       </c>
-      <c r="J51" s="52" t="s">
+      <c r="J51" s="35" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="52" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K51">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="8">
         <v>12</v>
       </c>
@@ -2968,18 +3106,21 @@
       <c r="I52" s="27">
         <v>36865</v>
       </c>
-      <c r="J52" s="52" t="s">
+      <c r="J52" s="35" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="53" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K52">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B53" s="8">
         <v>13</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D53" s="42">
+      <c r="D53" s="38">
         <v>3</v>
       </c>
       <c r="E53" s="11" t="s">
@@ -2991,24 +3132,27 @@
       <c r="G53" s="11">
         <v>219990304005</v>
       </c>
-      <c r="H53" s="38" t="s">
+      <c r="H53" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I53" s="28">
         <v>36386</v>
       </c>
-      <c r="J53" s="52" t="s">
+      <c r="J53" s="35" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="54" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K53">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B54" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D54" s="44"/>
+      <c r="D54" s="39"/>
       <c r="E54" s="1" t="s">
         <v>75</v>
       </c>
@@ -3018,22 +3162,25 @@
       <c r="G54" s="1">
         <v>119680190401</v>
       </c>
-      <c r="H54" s="40"/>
+      <c r="H54" s="44"/>
       <c r="I54" s="29">
         <v>25143</v>
       </c>
-      <c r="J54" s="52" t="s">
+      <c r="J54" s="35" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="55" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K54">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D55" s="43"/>
+      <c r="D55" s="40"/>
       <c r="E55" s="14" t="s">
         <v>76</v>
       </c>
@@ -3043,22 +3190,25 @@
       <c r="G55" s="14">
         <v>219710258429</v>
       </c>
-      <c r="H55" s="39"/>
+      <c r="H55" s="45"/>
       <c r="I55" s="30">
         <v>26126</v>
       </c>
-      <c r="J55" s="52" t="s">
+      <c r="J55" s="35" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="56" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K55">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B56" s="8">
         <v>14</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="42">
+      <c r="D56" s="38">
         <v>3</v>
       </c>
       <c r="E56" s="11" t="s">
@@ -3070,24 +3220,27 @@
       <c r="G56" s="11">
         <v>120000193714</v>
       </c>
-      <c r="H56" s="38" t="s">
+      <c r="H56" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I56" s="28">
         <v>36856</v>
       </c>
-      <c r="J56" s="52" t="s">
+      <c r="J56" s="35" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="57" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K56">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B57" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D57" s="44"/>
+      <c r="D57" s="39"/>
       <c r="E57" s="1" t="s">
         <v>75</v>
       </c>
@@ -3097,22 +3250,25 @@
       <c r="G57" s="1">
         <v>119660324286</v>
       </c>
-      <c r="H57" s="40"/>
+      <c r="H57" s="44"/>
       <c r="I57" s="29">
         <v>24171</v>
       </c>
-      <c r="J57" s="52" t="s">
+      <c r="J57" s="35" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="58" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K57">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D58" s="43"/>
+      <c r="D58" s="40"/>
       <c r="E58" s="14" t="s">
         <v>76</v>
       </c>
@@ -3122,22 +3278,25 @@
       <c r="G58" s="14">
         <v>219750238942</v>
       </c>
-      <c r="H58" s="39"/>
+      <c r="H58" s="45"/>
       <c r="I58" s="30">
         <v>27685</v>
       </c>
-      <c r="J58" s="52" t="s">
+      <c r="J58" s="35" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="59" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K58">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B59" s="8">
         <v>15</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D59" s="42">
+      <c r="D59" s="38">
         <v>3</v>
       </c>
       <c r="E59" s="11" t="s">
@@ -3149,24 +3308,27 @@
       <c r="G59" s="11">
         <v>120000473878</v>
       </c>
-      <c r="H59" s="38" t="s">
+      <c r="H59" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I59" s="28">
         <v>36763</v>
       </c>
-      <c r="J59" s="52" t="s">
+      <c r="J59" s="35" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="60" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K59">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B60" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D60" s="44"/>
+      <c r="D60" s="39"/>
       <c r="E60" s="1" t="s">
         <v>75</v>
       </c>
@@ -3176,22 +3338,25 @@
       <c r="G60" s="1">
         <v>119550131716</v>
       </c>
-      <c r="H60" s="40"/>
+      <c r="H60" s="44"/>
       <c r="I60" s="29">
         <v>20090</v>
       </c>
-      <c r="J60" s="52" t="s">
+      <c r="J60" s="35" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="61" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K60">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C61" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D61" s="43"/>
+      <c r="D61" s="40"/>
       <c r="E61" s="14" t="s">
         <v>76</v>
       </c>
@@ -3201,22 +3366,25 @@
       <c r="G61" s="14">
         <v>219720336265</v>
       </c>
-      <c r="H61" s="39"/>
+      <c r="H61" s="45"/>
       <c r="I61" s="30">
         <v>26299</v>
       </c>
-      <c r="J61" s="52" t="s">
+      <c r="J61" s="35" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="62" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K61">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B62" s="8">
         <v>16</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D62" s="42">
+      <c r="D62" s="38">
         <v>3</v>
       </c>
       <c r="E62" s="11" t="s">
@@ -3228,24 +3396,27 @@
       <c r="G62" s="11">
         <v>220010090316</v>
       </c>
-      <c r="H62" s="38" t="s">
+      <c r="H62" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I62" s="28">
         <v>36984</v>
       </c>
-      <c r="J62" s="52" t="s">
+      <c r="J62" s="35" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="63" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K62">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B63" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D63" s="44"/>
+      <c r="D63" s="39"/>
       <c r="E63" s="1" t="s">
         <v>75</v>
       </c>
@@ -3255,22 +3426,25 @@
       <c r="G63" s="1">
         <v>119680155965</v>
       </c>
-      <c r="H63" s="40"/>
+      <c r="H63" s="44"/>
       <c r="I63" s="29">
         <v>24845</v>
       </c>
-      <c r="J63" s="52" t="s">
+      <c r="J63" s="35" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="64" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K63">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D64" s="43"/>
+      <c r="D64" s="40"/>
       <c r="E64" s="14" t="s">
         <v>76</v>
       </c>
@@ -3280,22 +3454,25 @@
       <c r="G64" s="14">
         <v>219710258184</v>
       </c>
-      <c r="H64" s="39"/>
+      <c r="H64" s="45"/>
       <c r="I64" s="30">
         <v>26143</v>
       </c>
-      <c r="J64" s="52" t="s">
+      <c r="J64" s="35" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="65" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K64">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B65" s="8">
         <v>17</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D65" s="42">
+      <c r="D65" s="38">
         <v>3</v>
       </c>
       <c r="E65" s="11" t="s">
@@ -3307,24 +3484,27 @@
       <c r="G65" s="11">
         <v>119860016965</v>
       </c>
-      <c r="H65" s="38" t="s">
+      <c r="H65" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I65" s="28">
         <v>31566</v>
       </c>
-      <c r="J65" s="52" t="s">
+      <c r="J65" s="35" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="66" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K65">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B66" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D66" s="44"/>
+      <c r="D66" s="39"/>
       <c r="E66" s="1" t="s">
         <v>75</v>
       </c>
@@ -3334,22 +3514,25 @@
       <c r="G66" s="1">
         <v>119440002676</v>
       </c>
-      <c r="H66" s="40"/>
+      <c r="H66" s="44"/>
       <c r="I66" s="29">
         <v>16072</v>
       </c>
-      <c r="J66" s="52" t="s">
+      <c r="J66" s="35" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="67" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K66">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C67" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="D67" s="46"/>
+      <c r="D67" s="51"/>
       <c r="E67" s="3" t="s">
         <v>76</v>
       </c>
@@ -3359,22 +3542,25 @@
       <c r="G67" s="3">
         <v>219480004563</v>
       </c>
-      <c r="H67" s="41"/>
+      <c r="H67" s="52"/>
       <c r="I67" s="32">
         <v>17533</v>
       </c>
-      <c r="J67" s="52" t="s">
+      <c r="J67" s="35" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="68" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K67">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B68" s="8">
         <v>18</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D68" s="42">
+      <c r="D68" s="38">
         <v>2</v>
       </c>
       <c r="E68" s="11" t="s">
@@ -3386,24 +3572,27 @@
       <c r="G68" s="11">
         <v>119670230050</v>
       </c>
-      <c r="H68" s="38" t="s">
+      <c r="H68" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I68" s="28">
         <v>24473</v>
       </c>
-      <c r="J68" s="52" t="s">
+      <c r="J68" s="35" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="69" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K68">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C69" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D69" s="43"/>
+      <c r="D69" s="40"/>
       <c r="E69" s="14" t="s">
         <v>24</v>
       </c>
@@ -3413,22 +3602,25 @@
       <c r="G69" s="14">
         <v>219710304322</v>
       </c>
-      <c r="H69" s="39"/>
+      <c r="H69" s="45"/>
       <c r="I69" s="30">
         <v>26206</v>
       </c>
-      <c r="J69" s="52" t="s">
+      <c r="J69" s="35" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="70" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K69">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B70" s="8">
         <v>19</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D70" s="42">
+      <c r="D70" s="38">
         <v>8</v>
       </c>
       <c r="E70" s="11" t="s">
@@ -3440,24 +3632,27 @@
       <c r="G70" s="11">
         <v>119790246560</v>
       </c>
-      <c r="H70" s="38" t="s">
+      <c r="H70" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I70" s="28">
         <v>28979</v>
       </c>
-      <c r="J70" s="52" t="s">
+      <c r="J70" s="35" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="71" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K70">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B71" s="8" t="s">
         <v>249</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D71" s="44"/>
+      <c r="D71" s="39"/>
       <c r="E71" s="1" t="s">
         <v>24</v>
       </c>
@@ -3467,22 +3662,25 @@
       <c r="G71" s="1">
         <v>219860094711</v>
       </c>
-      <c r="H71" s="40"/>
+      <c r="H71" s="44"/>
       <c r="I71" s="29">
         <v>31595</v>
       </c>
-      <c r="J71" s="52" t="s">
+      <c r="J71" s="35" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="72" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K71">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B72" s="8" t="s">
         <v>250</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D72" s="44"/>
+      <c r="D72" s="39"/>
       <c r="E72" s="1" t="s">
         <v>90</v>
       </c>
@@ -3492,22 +3690,25 @@
       <c r="G72" s="1">
         <v>220090493294</v>
       </c>
-      <c r="H72" s="40"/>
+      <c r="H72" s="44"/>
       <c r="I72" s="29">
         <v>40135</v>
       </c>
-      <c r="J72" s="52" t="s">
+      <c r="J72" s="35" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="73" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K72">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B73" s="8" t="s">
         <v>251</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D73" s="44"/>
+      <c r="D73" s="39"/>
       <c r="E73" s="1" t="s">
         <v>90</v>
       </c>
@@ -3517,22 +3718,25 @@
       <c r="G73" s="1">
         <v>220120830053</v>
       </c>
-      <c r="H73" s="40"/>
+      <c r="H73" s="44"/>
       <c r="I73" s="29">
         <v>41069</v>
       </c>
-      <c r="J73" s="52" t="s">
+      <c r="J73" s="35" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="74" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K73">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B74" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C74" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D74" s="44"/>
+      <c r="D74" s="39"/>
       <c r="E74" s="1" t="s">
         <v>90</v>
       </c>
@@ -3542,22 +3746,25 @@
       <c r="G74" s="1">
         <v>220140376423</v>
       </c>
-      <c r="H74" s="40"/>
+      <c r="H74" s="44"/>
       <c r="I74" s="29">
         <v>41676</v>
       </c>
-      <c r="J74" s="52" t="s">
+      <c r="J74" s="35" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="75" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K74">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B75" s="8" t="s">
         <v>253</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D75" s="44"/>
+      <c r="D75" s="39"/>
       <c r="E75" s="1" t="s">
         <v>90</v>
       </c>
@@ -3567,22 +3774,25 @@
       <c r="G75" s="1">
         <v>220180438428</v>
       </c>
-      <c r="H75" s="40"/>
+      <c r="H75" s="44"/>
       <c r="I75" s="29">
         <v>43268</v>
       </c>
-      <c r="J75" s="52" t="s">
+      <c r="J75" s="35" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="76" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K75">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B76" s="8" t="s">
         <v>254</v>
       </c>
       <c r="C76" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D76" s="44"/>
+      <c r="D76" s="39"/>
       <c r="E76" s="1" t="s">
         <v>25</v>
       </c>
@@ -3592,22 +3802,25 @@
       <c r="G76" s="1">
         <v>119440041466</v>
       </c>
-      <c r="H76" s="40"/>
+      <c r="H76" s="44"/>
       <c r="I76" s="29">
         <v>16072</v>
       </c>
-      <c r="J76" s="52" t="s">
+      <c r="J76" s="35" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="77" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K76">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="9" t="s">
         <v>255</v>
       </c>
       <c r="C77" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D77" s="43"/>
+      <c r="D77" s="40"/>
       <c r="E77" s="14" t="s">
         <v>26</v>
       </c>
@@ -3617,22 +3830,25 @@
       <c r="G77" s="14">
         <v>219560085222</v>
       </c>
-      <c r="H77" s="39"/>
+      <c r="H77" s="45"/>
       <c r="I77" s="30">
         <v>20455</v>
       </c>
-      <c r="J77" s="52" t="s">
+      <c r="J77" s="35" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="78" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="K77">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" ht="18" x14ac:dyDescent="0.25">
       <c r="B78" s="5">
         <v>20</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D78" s="42">
+      <c r="D78" s="38">
         <v>2</v>
       </c>
       <c r="E78" s="11" t="s">
@@ -3644,24 +3860,27 @@
       <c r="G78" s="11">
         <v>119970267646</v>
       </c>
-      <c r="H78" s="38" t="s">
+      <c r="H78" s="43" t="s">
         <v>171</v>
       </c>
       <c r="I78" s="28">
         <v>35793</v>
       </c>
-      <c r="J78" s="52" t="s">
+      <c r="J78" s="35" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="79" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K78">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="33" t="s">
         <v>249</v>
       </c>
       <c r="C79" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D79" s="43"/>
+      <c r="D79" s="40"/>
       <c r="E79" s="15" t="s">
         <v>76</v>
       </c>
@@ -3671,15 +3890,18 @@
       <c r="G79" s="17">
         <v>219680183280</v>
       </c>
-      <c r="H79" s="39"/>
+      <c r="H79" s="45"/>
       <c r="I79" s="30">
         <v>24911</v>
       </c>
-      <c r="J79" s="52" t="s">
+      <c r="J79" s="35" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="K79">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" s="6"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
@@ -3687,7 +3909,7 @@
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
@@ -3695,7 +3917,7 @@
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
       <c r="D82" s="6"/>
@@ -3703,7 +3925,7 @@
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
@@ -3711,7 +3933,7 @@
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
       <c r="D84" s="6"/>
@@ -3719,7 +3941,7 @@
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
@@ -3727,7 +3949,7 @@
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
@@ -3735,7 +3957,7 @@
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
     </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
@@ -3743,7 +3965,7 @@
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
@@ -3751,7 +3973,7 @@
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
@@ -3759,7 +3981,7 @@
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
     </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
@@ -3767,7 +3989,7 @@
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
@@ -3775,7 +3997,7 @@
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
     </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
       <c r="D92" s="6"/>
@@ -3783,7 +4005,7 @@
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
     </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
       <c r="D93" s="6"/>
@@ -3791,7 +4013,7 @@
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
@@ -3799,7 +4021,7 @@
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
     </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
@@ -3807,7 +4029,7 @@
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
     </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
       <c r="D96" s="6"/>
@@ -3815,7 +4037,7 @@
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
@@ -3823,7 +4045,7 @@
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
@@ -3831,7 +4053,7 @@
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
@@ -3841,6 +4063,29 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="H21:H26"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="H70:H77"/>
+    <mergeCell ref="H78:H79"/>
+    <mergeCell ref="H53:H55"/>
+    <mergeCell ref="H56:H58"/>
+    <mergeCell ref="H59:H61"/>
+    <mergeCell ref="H62:H64"/>
+    <mergeCell ref="H65:H67"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="D48:D51"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="D21:D26"/>
+    <mergeCell ref="D38:D44"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="D62:D64"/>
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="D65:D67"/>
+    <mergeCell ref="D18:D20"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="D70:D77"/>
@@ -3857,29 +4102,6 @@
     <mergeCell ref="H38:H44"/>
     <mergeCell ref="H45:H47"/>
     <mergeCell ref="H48:H51"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="D48:D51"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="D45:D47"/>
-    <mergeCell ref="D56:D58"/>
-    <mergeCell ref="D21:D26"/>
-    <mergeCell ref="D38:D44"/>
-    <mergeCell ref="D59:D61"/>
-    <mergeCell ref="D62:D64"/>
-    <mergeCell ref="D53:D55"/>
-    <mergeCell ref="D65:D67"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="H21:H26"/>
-    <mergeCell ref="H68:H69"/>
-    <mergeCell ref="H70:H77"/>
-    <mergeCell ref="H78:H79"/>
-    <mergeCell ref="H53:H55"/>
-    <mergeCell ref="H56:H58"/>
-    <mergeCell ref="H59:H61"/>
-    <mergeCell ref="H62:H64"/>
-    <mergeCell ref="H65:H67"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
